--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_690_Seychelles.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_690_Seychelles.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R85e8a51082554e54"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rb759a90f8c304b9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Ra4778e944d5847ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R6f7ba6713a494012"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R3d5f6882f2244c57"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R5839f53dd15a4498"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R1e36c6d83d914ba5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rebefac1a01a6492a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rf68cf48f92c3478f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R9a0e1b0183e74cdc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Re0a55f89fd80457c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Raf170ab616cd4971"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ690CommercialTable" displayName="EEZ690CommercialTable" ref="A1:O8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O8"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ690CommercialTable" displayName="EEZ690CommercialTable" ref="A1:E8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E8"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ690FunctionalTable" displayName="EEZ690FunctionalTable" ref="A1:O19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O19"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ690FunctionalTable" displayName="EEZ690FunctionalTable" ref="A1:E19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E19"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ690ValidationTable" displayName="EEZ690ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ690ValidationTable" displayName="EEZ690ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -8600,7 +8554,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R234902e2ddd046d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3440194c117d4ad3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8610,20 +8564,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -8631,444 +8575,155 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.485832584</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.34</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>218.77616239495518</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.485832584</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>218.7761623949552</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$119,A2,'Species'!$U$2:$U$119))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>106.28858829394471</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.34</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>218.77616239495518</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>106.28858829394471</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>90.25</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.9199999999999995</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>831.76377110267</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>90.25</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$119,A3,'Species'!$U$2:$U$119))</x:f>
-        <x:v>75066.68034201604</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.9199999999999995</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>831.76377110267</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>75066.68034201597</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>7.275957614183426e-11</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>9.692659354367321e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>0.5490293397</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.15</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>141.2537544622754</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>0.5490293397</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>141.2537544622754</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$119,A4,'Species'!$U$2:$U$119))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>77.55245554256899</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.15</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>141.2537544622754</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>77.55245554256899</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>2051.8335112452996</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.2637443074177708</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>183.5457392422631</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>2051.8335112452996</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>196.2564701123018</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$119,A5,'Species'!$U$2:$U$119))</x:f>
-        <x:v>402685.60217513243</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.2637443074177708</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>183.5457392422631</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>376605.29862356686</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>26080.303551565565</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0692510265970367</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.06925102659703666</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>6869.5041555359</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.632151240711314</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>428.6977860976242</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>6869.5041555359</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>1202.600686579853</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$119,A6,'Species'!$U$2:$U$119))</x:f>
-        <x:v>8261270.413910626</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.632151240711314</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>428.6977860976242</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>2944941.22306667</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>5316329.190843957</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>2.805241187567023</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>1.8052411875670231</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>6187.6109181434995</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>4.353717878459852</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>2257.9684973707203</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>6187.6109181434995</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>2315.608147909859</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$119,A7,'Species'!$U$2:$U$119))</x:f>
-        <x:v>14328082.25814909</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>4.353717878459852</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>2257.9684973707203</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>13971430.52715514</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>356651.7309939489</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.025527216436481</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.025527216436481127</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>3510.0037606352</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.441861830747577</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2766.0614927355505</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>3510.0037606352</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2793.1843051528604</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$119,A8,'Species'!$U$2:$U$119))</x:f>
-        <x:v>9804087.415233757</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.441861830747577</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2766.0614927355505</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>9708886.241649996</x:v>
       </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>95201.17358376086</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0098055710216645</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.009805571021664551</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G8">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O8">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re891a30907e04450"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb5b52040962f4e3d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9078,20 +8733,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -9099,1038 +8744,364 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>86.903650441</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.598193780113684</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>396.45489106601656</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>86.903650441</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>396.4889985465948</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$119,A2,'Species'!$U$2:$U$119))</x:f>
-        <x:v>34456.34133339543</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.598193780113684</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>396.45489106601656</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>34453.37726882583</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>2.964064569598122</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.000086031176174</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.00008603117617383978</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>74.2922279633</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>31.622776601683793</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>74.2922279633</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>31.622776601683793</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$119,A3,'Species'!$U$2:$U$119))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2349.3265281248014</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.5</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>31.622776601683793</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>2349.3265281248014</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>41.638680433</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.8135043977592127</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>650.885201810406</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>41.638680433</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>1958.756920143474</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$119,A4,'Species'!$U$2:$U$119))</x:f>
-        <x:v>81560.0534437814</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.8135043977592127</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>650.885201810406</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>27102.000916752208</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>54458.0525270292</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>3.009373872220916</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>2.009373872220916</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>0.16170295419999997</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.9</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>794.3282347242813</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>0.16170295419999997</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>794.3282347242812</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$119,A5,'Species'!$U$2:$U$119))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>128.44522215938727</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.9</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>128.44522215938727</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>2887.1243770501005</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.4566094214906595</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2861.603257310646</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>2887.1243770501005</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2886.858066448095</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$119,A6,'Species'!$U$2:$U$119))</x:f>
-        <x:v>8334718.296726014</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.4566094214906595</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2861.603257310646</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>8261804.521627537</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>72913.77509847749</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0088254055040404</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.008825405504040396</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>36.7124415294</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.599817851816157</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>397.94023476102524</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>36.7124415294</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>398.400896373437</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$119,A7,'Species'!$U$2:$U$119))</x:f>
-        <x:v>14626.269613370354</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.599817851816157</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>397.94023476102524</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>14609.35760085985</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>16.9120125105037</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0011576150692285</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.0011576150692285282</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1502.9189697790002</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.451731523133899</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2829.6421961430747</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1502.9189697790002</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2891.794329623461</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$119,A8,'Species'!$U$2:$U$119))</x:f>
-        <x:v>4346132.554690447</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.451731523133899</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2829.6421961430747</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>4252722.934270537</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>93409.62041990925</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0219646616682145</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.021964661668214612</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>6150.8984766141</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.358217629309651</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2281.485060583288</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>6150.8984766141</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2327.0512499850074</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$119,A9,'Species'!$U$2:$U$119))</x:f>
-        <x:v>14313455.988535719</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.358217629309651</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2281.485060583288</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>14033182.983559575</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>280273.00497614406</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0199721620750257</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.019972162075025664</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>90.25</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.9199999999999995</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>831.76377110267</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>90.25</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>831.7637711026708</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$119,A10,'Species'!$U$2:$U$119))</x:f>
-        <x:v>75066.68034201604</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.9199999999999995</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>831.76377110267</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>75066.68034201597</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>7.275957614183426e-11</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0000000000000009</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>9.692659354367321e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>58.446862012</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.3643158327984866</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>231.37468089659754</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>58.446862012</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>240.4967352585486</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$119,A11,'Species'!$U$2:$U$119))</x:f>
-        <x:v>14056.279499992885</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.3643158327984866</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>231.37468089659754</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>13523.124047433968</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>533.1554525589163</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0394254649065415</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.03942546490654157</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1942.6656850681</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.314728039299801</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>206.4087193498245</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1942.6656850681</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>228.55758966978786</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$119,A12,'Species'!$U$2:$U$119))</x:f>
-        <x:v>444010.9865133721</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.314728039299801</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>206.4087193498245</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>400983.136179756</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>43027.85033361608</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.1073058850892104</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.10730588508921034</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>2655.6813687192</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.5709651056260645</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>372.3617868013572</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>2655.6813687192</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>820.355620882565</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$119,A13,'Species'!$U$2:$U$119))</x:f>
-        <x:v>2178603.138101899</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.5709651056260645</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>372.3617868013572</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>988874.2596313552</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1189728.8784705438</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>2.203114417109073</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>1.2031144171090729</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>3136.7005675855003</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.4297986553935305</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>269.0287262371851</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>3136.7005675855003</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>960.6841640946475</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$119,A14,'Species'!$U$2:$U$119))</x:f>
-        <x:v>3013378.5627860827</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.4297986553935305</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>269.0287262371851</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>843862.5582849826</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>2169516.0045011</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>3.5709352585927014</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>2.5709352585927014</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>3.7670509591999997</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.24</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>173.78008287493762</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>3.7670509591999997</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$119,A15,'Species'!$U$2:$U$119))</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>654.6384278838892</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.24</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
-        <x:v>654.6384278838892</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>1.9658548138999998</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.5393358405301507</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>346.2069966924241</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>1.9658548138999998</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>353.5218556005772</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$119,A16,'Species'!$U$2:$U$119))</x:f>
-        <x:v>694.9726416512553</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.5393358405301507</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>346.2069966924241</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>680.5926910536633</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>14.379950597592028</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.021128570416073</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.021128570416073127</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>3.2481016056</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>4.156408654262573</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>1433.5361667709876</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>3.2481016056</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>1729.5456094147191</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$119,A17,'Species'!$U$2:$U$119))</x:f>
-        <x:v>5617.73987089838</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>4.156408654262573</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>1433.5361667709876</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>4656.271124974514</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>961.4687459238658</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.2064889951890696</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.20648899518906952</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>36.312160616300005</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.161082940614124</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>144.9048563259339</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>36.312160616300005</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>324.6401184073221</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$119,A18,'Species'!$U$2:$U$119))</x:f>
-        <x:v>11788.384122101332</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.161082940614124</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>144.9048563259339</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>5261.808416989188</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>6526.575705112144</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>2.2403674151341786</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>1.2403674151341786</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>0.5490293397</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.15</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>141.2537544622754</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>0.5490293397</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>141.2537544622754</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$119,A19,'Species'!$U$2:$U$119))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>77.55245554256899</x:v>
       </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.15</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>141.2537544622754</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>77.55245554256899</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G19">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O19">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R26778592c3844357"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4543179e9c704b12"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10305,7 +9276,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -10404,7 +9375,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>32871376.21085445</x:v>
+        <x:v>27077113.811881226</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10418,7 +9389,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>32871376.21085445</x:v>
+        <x:v>28959993.568596356</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10432,7 +9403,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-7.450580596923828e-9</x:v>
+        <x:v>-5794262.39897323</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10446,7 +9417,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-7.450580596923828e-9</x:v>
+        <x:v>-3911382.6422581</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -10457,9 +9428,9 @@
         <x:v>EEZ_690</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -10471,47 +9442,19 @@
         <x:v>EEZ_690</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_690</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_690</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cd716d56b6f4211"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fe587e741d54d33"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10558,7 +9501,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
